--- a/artfynd/A 72433-2021 artfynd.xlsx
+++ b/artfynd/A 72433-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120293925</v>
       </c>
       <c r="B2" t="n">
-        <v>56514</v>
+        <v>56524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>120294186</v>
       </c>
       <c r="B3" t="n">
-        <v>57986</v>
+        <v>57996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 72433-2021 artfynd.xlsx
+++ b/artfynd/A 72433-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120293925</v>
+        <v>120294186</v>
       </c>
       <c r="B2" t="n">
-        <v>56524</v>
+        <v>57996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,11 +708,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -723,14 +719,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KantC, Sörfjärden, Gnarp, Hls</t>
+          <t>KantD, Sörfjärden, Gnarp, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624710</v>
+        <v>624517</v>
       </c>
       <c r="R2" t="n">
-        <v>6877332</v>
+        <v>6877368</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120294186</v>
+        <v>120293925</v>
       </c>
       <c r="B3" t="n">
-        <v>57996</v>
+        <v>56524</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +797,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,7 +818,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -833,14 +833,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KantD, Sörfjärden, Gnarp, Hls</t>
+          <t>KantC, Sörfjärden, Gnarp, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624517</v>
+        <v>624710</v>
       </c>
       <c r="R3" t="n">
-        <v>6877368</v>
+        <v>6877332</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>

--- a/artfynd/A 72433-2021 artfynd.xlsx
+++ b/artfynd/A 72433-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120294186</v>
+        <v>120293925</v>
       </c>
       <c r="B2" t="n">
-        <v>57996</v>
+        <v>56524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,7 +708,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -719,14 +723,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KantD, Sörfjärden, Gnarp, Hls</t>
+          <t>KantC, Sörfjärden, Gnarp, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624517</v>
+        <v>624710</v>
       </c>
       <c r="R2" t="n">
-        <v>6877368</v>
+        <v>6877332</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120293925</v>
+        <v>120294186</v>
       </c>
       <c r="B3" t="n">
-        <v>56524</v>
+        <v>57996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -818,11 +822,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -833,14 +833,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KantC, Sörfjärden, Gnarp, Hls</t>
+          <t>KantD, Sörfjärden, Gnarp, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624710</v>
+        <v>624517</v>
       </c>
       <c r="R3" t="n">
-        <v>6877332</v>
+        <v>6877368</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>

--- a/artfynd/A 72433-2021 artfynd.xlsx
+++ b/artfynd/A 72433-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>120293925</v>
       </c>
       <c r="B2" t="n">
-        <v>56536</v>
+        <v>56692</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,17 +723,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KantC, Sörfjärden, Gnarp, Hls</t>
+          <t>Rundamyren, Hårte, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>624710</v>
       </c>
       <c r="R2" t="n">
-        <v>6877332</v>
+        <v>6877333</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120294186</v>
+        <v>120293900</v>
       </c>
       <c r="B3" t="n">
-        <v>58008</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,26 +805,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -833,17 +841,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>KantD, Sörfjärden, Gnarp, Hls</t>
+          <t>Rundamyren, Vettberget, Gnarp, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624517</v>
+        <v>624536</v>
       </c>
       <c r="R3" t="n">
-        <v>6877368</v>
+        <v>6877311</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,6 +904,116 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120294186</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58008</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>KantD, Sörfjärden, Gnarp, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>624517</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6877368</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 72433-2021 artfynd.xlsx
+++ b/artfynd/A 72433-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120293925</v>
+        <v>120293900</v>
       </c>
       <c r="B2" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,7 +709,11 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
@@ -723,14 +722,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rundamyren, Hårte, Jättendal, Hls</t>
+          <t>Rundamyren, Vettberget, Gnarp, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624710</v>
+        <v>624536</v>
       </c>
       <c r="R2" t="n">
-        <v>6877333</v>
+        <v>6877311</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120293900</v>
+        <v>120293925</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,21 +799,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,11 +822,7 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -841,14 +831,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rundamyren, Vettberget, Gnarp, Hls</t>
+          <t>Rundamyren, Hårte, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624536</v>
+        <v>624710</v>
       </c>
       <c r="R3" t="n">
-        <v>6877311</v>
+        <v>6877333</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,12 +900,7 @@
         <v>120294186</v>
       </c>
       <c r="B4" t="n">
-        <v>58008</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 72433-2021 artfynd.xlsx
+++ b/artfynd/A 72433-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120293900</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120293925</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,8 +1014,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120294186</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>